--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.24217041485412</v>
+        <v>8.001852692413795</v>
       </c>
       <c r="D2" t="n">
-        <v>30.52756655756464</v>
+        <v>4.960729565604255</v>
       </c>
       <c r="E2" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F2" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.77720154304445</v>
+        <v>5.651295250744723</v>
       </c>
       <c r="D3" t="n">
-        <v>18.06790705591225</v>
+        <v>2.936034896585741</v>
       </c>
       <c r="E3" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F3" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.58017264439963</v>
+        <v>3.99427805471494</v>
       </c>
       <c r="D4" t="n">
-        <v>21.65764341141261</v>
+        <v>3.51936705435455</v>
       </c>
       <c r="E4" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F4" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.0469204709887</v>
+        <v>4.557624576535664</v>
       </c>
       <c r="D5" t="n">
-        <v>9.327640410503395</v>
+        <v>1.515741566706802</v>
       </c>
       <c r="E5" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F5" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.17386020363778</v>
+        <v>3.440752283091139</v>
       </c>
       <c r="D6" t="n">
-        <v>13.65044258816354</v>
+        <v>2.218196920576576</v>
       </c>
       <c r="E6" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F6" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.44382759339172</v>
+        <v>6.409621983926155</v>
       </c>
       <c r="D7" t="n">
-        <v>39.970014328861</v>
+        <v>6.495127328439913</v>
       </c>
       <c r="E7" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F7" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.89875585046591</v>
+        <v>5.18354782570071</v>
       </c>
       <c r="D8" t="n">
-        <v>29.15047234787023</v>
+        <v>4.736951756528914</v>
       </c>
       <c r="E8" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F8" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.98668306814989</v>
+        <v>2.760335998574357</v>
       </c>
       <c r="D9" t="n">
-        <v>10.03797661442357</v>
+        <v>1.63117119984383</v>
       </c>
       <c r="E9" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F9" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.87966904565344</v>
+        <v>4.042946219918684</v>
       </c>
       <c r="D10" t="n">
-        <v>24.55786842394923</v>
+        <v>3.990653618891749</v>
       </c>
       <c r="E10" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F10" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.64723799231427</v>
+        <v>2.705176173751069</v>
       </c>
       <c r="D11" t="n">
-        <v>16.7317132048267</v>
+        <v>2.718903395784339</v>
       </c>
       <c r="E11" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F11" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.24094119848775</v>
+        <v>5.88915294475426</v>
       </c>
       <c r="D12" t="n">
-        <v>35.25669171742528</v>
+        <v>5.729212404081609</v>
       </c>
       <c r="E12" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F12" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.59743365071975</v>
+        <v>4.48458296824196</v>
       </c>
       <c r="D13" t="n">
-        <v>21.11717839317396</v>
+        <v>3.431541488890768</v>
       </c>
       <c r="E13" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F13" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.818793028754317</v>
+        <v>1.433053867172577</v>
       </c>
       <c r="D14" t="n">
-        <v>7.424333046221161</v>
+        <v>1.206454120010939</v>
       </c>
       <c r="E14" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F14" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.05127065356239</v>
+        <v>5.858331481203889</v>
       </c>
       <c r="D15" t="n">
-        <v>34.53492763844442</v>
+        <v>5.611925741247219</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F15" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>26.9605611555418</v>
+        <v>4.381091187775542</v>
       </c>
       <c r="D16" t="n">
-        <v>25.58905152237231</v>
+        <v>4.158220872385501</v>
       </c>
       <c r="E16" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F16" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.943333914102</v>
+        <v>4.378291761041575</v>
       </c>
       <c r="D17" t="n">
-        <v>23.58795773895615</v>
+        <v>3.833043132580374</v>
       </c>
       <c r="E17" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F17" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>40.96927483201301</v>
+        <v>6.657507160202114</v>
       </c>
       <c r="D18" t="n">
-        <v>39.53141500001542</v>
+        <v>6.423854937502506</v>
       </c>
       <c r="E18" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F18" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>47.98151569061945</v>
+        <v>7.796996299725661</v>
       </c>
       <c r="D19" t="n">
-        <v>46.46118409593442</v>
+        <v>7.549942415589344</v>
       </c>
       <c r="E19" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F19" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.29169530385523</v>
+        <v>4.434900486876475</v>
       </c>
       <c r="D20" t="n">
-        <v>26.84358012065659</v>
+        <v>4.362081769606696</v>
       </c>
       <c r="E20" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F20" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>43.49749139857124</v>
+        <v>7.068342352267827</v>
       </c>
       <c r="D21" t="n">
-        <v>42.61276883489406</v>
+        <v>6.924574935670284</v>
       </c>
       <c r="E21" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F21" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>46.0091504784055</v>
+        <v>7.476486952740895</v>
       </c>
       <c r="D22" t="n">
-        <v>44.68830251580979</v>
+        <v>7.261849158819091</v>
       </c>
       <c r="E22" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F22" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>45.43562956565362</v>
+        <v>7.383289804418713</v>
       </c>
       <c r="D23" t="n">
-        <v>44.33714372339248</v>
+        <v>7.204785855051278</v>
       </c>
       <c r="E23" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F23" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>48.97838513865279</v>
+        <v>7.958987585031078</v>
       </c>
       <c r="D24" t="n">
-        <v>48.25824052055171</v>
+        <v>7.841964084589653</v>
       </c>
       <c r="E24" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F24" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>59.55317212784155</v>
+        <v>9.677390470774252</v>
       </c>
       <c r="D25" t="n">
-        <v>58.16959357844375</v>
+        <v>9.452558956497111</v>
       </c>
       <c r="E25" t="n">
-        <v>12.15035627363105</v>
+        <v>1.974432894465046</v>
       </c>
       <c r="F25" t="n">
-        <v>13.51689243445395</v>
+        <v>2.196495020598767</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
